--- a/WorkLog_2026-03.xlsx
+++ b/WorkLog_2026-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyearick.CRP\OneDrive - CRP Industries Inc\CRPAF\PycharmProjects\CRPUtils\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2335B00-90C2-4A57-9126-03590209EB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348600B1-719A-47AA-9976-D069C1A7E24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="25575" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3186,7 +3186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3195,11 +3195,864 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="282">
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5488,32 +6341,32 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F870FB5F-F4BB-4E27-8C97-D858387F0FD1}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:F152" firstHeaderRow="1" firstDataRow="1" firstDataCol="5"/>
   <pivotFields count="10">
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="24">
+        <item x="23"/>
+        <item x="22"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="15"/>
+        <item x="14"/>
+        <item x="13"/>
+        <item x="12"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -5967,773 +6820,6 @@
   <rowItems count="149">
     <i>
       <x/>
-      <x v="102"/>
-      <x v="107"/>
-      <x v="1"/>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="106"/>
-      <x v="103"/>
-      <x/>
-      <x v="137"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="57"/>
-      <x v="63"/>
-      <x v="1"/>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="64"/>
-      <x v="66"/>
-      <x/>
-      <x v="146"/>
-    </i>
-    <i r="1">
-      <x v="111"/>
-      <x v="110"/>
-      <x v="1"/>
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="113"/>
-      <x v="112"/>
-      <x v="1"/>
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="122"/>
-      <x v="121"/>
-      <x/>
-      <x v="122"/>
-    </i>
-    <i r="1">
-      <x v="126"/>
-      <x v="125"/>
-      <x/>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x v="7"/>
-      <x v="5"/>
-      <x v="1"/>
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="93"/>
-      <x v="95"/>
-      <x v="1"/>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x/>
-      <x v="2"/>
-      <x v="1"/>
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-      <x v="13"/>
-      <x v="1"/>
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-      <x v="17"/>
-      <x v="1"/>
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="20"/>
-      <x v="21"/>
-      <x/>
-      <x v="92"/>
-    </i>
-    <i r="1">
-      <x v="23"/>
-      <x v="25"/>
-      <x v="1"/>
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="34"/>
-      <x v="38"/>
-      <x v="1"/>
-      <x v="14"/>
-    </i>
-    <i r="1">
-      <x v="43"/>
-      <x v="41"/>
-      <x/>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="33"/>
-      <x v="33"/>
-      <x v="1"/>
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="35"/>
-      <x v="34"/>
-      <x/>
-      <x v="82"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-      <x v="48"/>
-      <x/>
-      <x v="85"/>
-    </i>
-    <i r="1">
-      <x v="55"/>
-      <x v="57"/>
-      <x v="1"/>
-      <x v="16"/>
-    </i>
-    <i r="1">
-      <x v="78"/>
-      <x v="86"/>
-      <x v="1"/>
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="83"/>
-      <x v="82"/>
-      <x/>
-      <x v="86"/>
-    </i>
-    <i r="1">
-      <x v="92"/>
-      <x v="92"/>
-      <x v="2"/>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="1"/>
-      <x/>
-      <x v="1"/>
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-      <x v="12"/>
-      <x v="1"/>
-      <x v="19"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-      <x v="18"/>
-      <x v="1"/>
-      <x v="20"/>
-    </i>
-    <i r="1">
-      <x v="20"/>
-      <x v="21"/>
-      <x/>
-      <x v="84"/>
-    </i>
-    <i r="1">
-      <x v="26"/>
-      <x v="45"/>
-      <x v="1"/>
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="66"/>
-      <x v="68"/>
-      <x v="2"/>
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="67"/>
-      <x v="70"/>
-      <x/>
-      <x v="106"/>
-    </i>
-    <i r="1">
-      <x v="98"/>
-      <x v="98"/>
-      <x/>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="6"/>
-      <x v="17"/>
-      <x v="18"/>
-      <x v="1"/>
-      <x v="23"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-      <x v="24"/>
-      <x v="1"/>
-      <x v="24"/>
-    </i>
-    <i r="1">
-      <x v="41"/>
-      <x v="44"/>
-      <x v="1"/>
-      <x v="25"/>
-    </i>
-    <i r="1">
-      <x v="50"/>
-      <x v="51"/>
-      <x v="2"/>
-      <x v="26"/>
-    </i>
-    <i r="1">
-      <x v="58"/>
-      <x v="59"/>
-      <x/>
-      <x v="109"/>
-    </i>
-    <i r="1">
-      <x v="82"/>
-      <x v="84"/>
-      <x v="1"/>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="7"/>
-      <x v="38"/>
-      <x v="36"/>
-      <x v="1"/>
-      <x v="29"/>
-    </i>
-    <i r="1">
-      <x v="48"/>
-      <x v="53"/>
-      <x v="1"/>
-      <x v="30"/>
-    </i>
-    <i r="1">
-      <x v="63"/>
-      <x v="65"/>
-      <x v="2"/>
-      <x v="28"/>
-    </i>
-    <i r="1">
-      <x v="68"/>
-      <x v="76"/>
-      <x/>
-      <x v="99"/>
-    </i>
-    <i r="1">
-      <x v="69"/>
-      <x v="71"/>
-      <x/>
-      <x v="119"/>
-    </i>
-    <i r="1">
-      <x v="76"/>
-      <x v="77"/>
-      <x v="1"/>
-      <x v="31"/>
-    </i>
-    <i r="1">
-      <x v="108"/>
-      <x v="104"/>
-      <x v="1"/>
-      <x v="32"/>
-    </i>
-    <i r="1">
-      <x v="109"/>
-      <x v="106"/>
-      <x/>
-      <x v="110"/>
-    </i>
-    <i>
-      <x v="8"/>
-      <x v="18"/>
-      <x v="19"/>
-      <x v="1"/>
-      <x v="33"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
-      <x v="20"/>
-      <x/>
-      <x v="83"/>
-    </i>
-    <i r="1">
-      <x v="39"/>
-      <x v="37"/>
-      <x/>
-      <x v="120"/>
-    </i>
-    <i r="1">
-      <x v="40"/>
-      <x v="39"/>
-      <x v="1"/>
-      <x v="34"/>
-    </i>
-    <i r="1">
-      <x v="60"/>
-      <x v="64"/>
-      <x v="1"/>
-      <x v="35"/>
-    </i>
-    <i r="1">
-      <x v="74"/>
-      <x v="78"/>
-      <x v="1"/>
-      <x v="36"/>
-    </i>
-    <i r="1">
-      <x v="88"/>
-      <x v="89"/>
-      <x v="1"/>
-      <x v="37"/>
-    </i>
-    <i r="1">
-      <x v="95"/>
-      <x v="95"/>
-      <x/>
-      <x v="94"/>
-    </i>
-    <i r="1">
-      <x v="97"/>
-      <x v="96"/>
-      <x v="1"/>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="9"/>
-      <x v="2"/>
-      <x v="1"/>
-      <x/>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="10"/>
-      <x v="8"/>
-      <x v="8"/>
-      <x/>
-      <x v="123"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-      <x v="10"/>
-      <x/>
-      <x v="96"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-      <x v="11"/>
-      <x v="1"/>
-      <x v="39"/>
-    </i>
-    <i r="1">
-      <x v="45"/>
-      <x v="43"/>
-      <x v="1"/>
-      <x v="40"/>
-    </i>
-    <i r="1">
-      <x v="56"/>
-      <x v="58"/>
-      <x/>
-      <x v="134"/>
-    </i>
-    <i r="1">
-      <x v="85"/>
-      <x v="86"/>
-      <x v="1"/>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="11"/>
-      <x v="15"/>
-      <x v="17"/>
-      <x v="1"/>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="12"/>
-      <x v="46"/>
-      <x v="49"/>
-      <x v="1"/>
-      <x v="43"/>
-    </i>
-    <i r="1">
-      <x v="61"/>
-      <x v="61"/>
-      <x v="2"/>
-      <x v="44"/>
-    </i>
-    <i r="1">
-      <x v="62"/>
-      <x v="62"/>
-      <x/>
-      <x v="141"/>
-    </i>
-    <i>
-      <x v="13"/>
-      <x v="14"/>
-      <x v="15"/>
-      <x/>
-      <x v="140"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-      <x v="18"/>
-      <x v="2"/>
-      <x v="45"/>
-    </i>
-    <i r="1">
-      <x v="86"/>
-      <x v="87"/>
-      <x v="1"/>
-      <x v="46"/>
-    </i>
-    <i r="1">
-      <x v="87"/>
-      <x v="88"/>
-      <x/>
-      <x v="111"/>
-    </i>
-    <i r="1">
-      <x v="90"/>
-      <x v="90"/>
-      <x/>
-      <x v="142"/>
-    </i>
-    <i r="1">
-      <x v="94"/>
-      <x v="94"/>
-      <x v="2"/>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="14"/>
-      <x v="81"/>
-      <x v="80"/>
-      <x/>
-      <x v="129"/>
-    </i>
-    <i>
-      <x v="15"/>
-      <x v="4"/>
-      <x v="4"/>
-      <x v="1"/>
-      <x v="48"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-      <x v="9"/>
-      <x v="1"/>
-      <x v="49"/>
-    </i>
-    <i r="1">
-      <x v="42"/>
-      <x v="40"/>
-      <x/>
-      <x v="107"/>
-    </i>
-    <i r="1">
-      <x v="65"/>
-      <x v="67"/>
-      <x/>
-      <x v="108"/>
-    </i>
-    <i r="1">
-      <x v="77"/>
-      <x v="79"/>
-      <x v="1"/>
-      <x v="50"/>
-    </i>
-    <i r="1">
-      <x v="84"/>
-      <x v="85"/>
-      <x/>
-      <x v="118"/>
-    </i>
-    <i r="1">
-      <x v="103"/>
-      <x v="102"/>
-      <x v="1"/>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="16"/>
-      <x v="13"/>
-      <x v="14"/>
-      <x/>
-      <x v="116"/>
-    </i>
-    <i r="1">
-      <x v="14"/>
-      <x v="16"/>
-      <x v="1"/>
-      <x v="52"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-      <x v="30"/>
-      <x v="1"/>
-      <x v="53"/>
-    </i>
-    <i r="1">
-      <x v="54"/>
-      <x v="56"/>
-      <x v="1"/>
-      <x v="54"/>
-    </i>
-    <i r="1">
-      <x v="63"/>
-      <x v="69"/>
-      <x v="1"/>
-      <x v="55"/>
-    </i>
-    <i r="1">
-      <x v="96"/>
-      <x v="97"/>
-      <x v="1"/>
-      <x v="56"/>
-    </i>
-    <i r="1">
-      <x v="107"/>
-      <x v="105"/>
-      <x v="1"/>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="17"/>
-      <x v="25"/>
-      <x v="26"/>
-      <x v="1"/>
-      <x v="58"/>
-    </i>
-    <i r="1">
-      <x v="32"/>
-      <x v="32"/>
-      <x v="2"/>
-      <x v="61"/>
-    </i>
-    <i r="1">
-      <x v="55"/>
-      <x v="57"/>
-      <x v="2"/>
-      <x v="62"/>
-    </i>
-    <i r="1">
-      <x v="73"/>
-      <x v="74"/>
-      <x v="1"/>
-      <x v="59"/>
-    </i>
-    <i r="1">
-      <x v="79"/>
-      <x v="81"/>
-      <x/>
-      <x v="130"/>
-    </i>
-    <i r="1">
-      <x v="80"/>
-      <x v="83"/>
-      <x v="1"/>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="18"/>
-      <x v="21"/>
-      <x v="23"/>
-      <x v="1"/>
-      <x v="63"/>
-    </i>
-    <i r="1">
-      <x v="30"/>
-      <x v="46"/>
-      <x v="1"/>
-      <x v="64"/>
-    </i>
-    <i r="1">
-      <x v="37"/>
-      <x v="35"/>
-      <x/>
-      <x v="144"/>
-    </i>
-    <i>
-      <x v="19"/>
-      <x v="29"/>
-      <x v="28"/>
-      <x/>
-      <x v="143"/>
-    </i>
-    <i r="1">
-      <x v="31"/>
-      <x v="31"/>
-      <x v="1"/>
-      <x v="65"/>
-    </i>
-    <i r="1">
-      <x v="71"/>
-      <x v="72"/>
-      <x/>
-      <x v="128"/>
-    </i>
-    <i r="1">
-      <x v="75"/>
-      <x v="75"/>
-      <x v="1"/>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="20"/>
-      <x v="5"/>
-      <x v="7"/>
-      <x v="1"/>
-      <x v="68"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-      <x v="6"/>
-      <x/>
-      <x v="138"/>
-    </i>
-    <i r="1">
-      <x v="44"/>
-      <x v="42"/>
-      <x/>
-      <x v="102"/>
-    </i>
-    <i r="1">
-      <x v="47"/>
-      <x v="47"/>
-      <x v="1"/>
-      <x v="69"/>
-    </i>
-    <i r="1">
-      <x v="49"/>
-      <x v="50"/>
-      <x/>
-      <x v="125"/>
-    </i>
-    <i r="1">
-      <x v="51"/>
-      <x v="52"/>
-      <x v="2"/>
-      <x v="67"/>
-    </i>
-    <i r="1">
-      <x v="52"/>
-      <x v="54"/>
-      <x/>
-      <x v="105"/>
-    </i>
-    <i r="1">
-      <x v="100"/>
-      <x v="100"/>
-      <x/>
-      <x v="131"/>
-    </i>
-    <i r="1">
-      <x v="101"/>
-      <x v="101"/>
-      <x/>
-      <x v="124"/>
-    </i>
-    <i r="1">
-      <x v="123"/>
-      <x v="123"/>
-      <x/>
-      <x v="127"/>
-    </i>
-    <i r="1">
-      <x v="124"/>
-      <x v="124"/>
-      <x/>
-      <x v="89"/>
-    </i>
-    <i r="1">
-      <x v="125"/>
-      <x v="126"/>
-      <x v="1"/>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="21"/>
-      <x v="89"/>
-      <x v="93"/>
-      <x v="1"/>
-      <x v="71"/>
-    </i>
-    <i r="1">
-      <x v="91"/>
-      <x v="91"/>
-      <x/>
-      <x v="135"/>
-    </i>
-    <i r="1">
-      <x v="118"/>
-      <x v="118"/>
-      <x v="1"/>
-      <x v="72"/>
-    </i>
-    <i r="1">
-      <x v="119"/>
-      <x v="119"/>
-      <x/>
-      <x v="117"/>
-    </i>
-    <i r="1">
-      <x v="120"/>
-      <x v="120"/>
-      <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="121"/>
-      <x v="121"/>
-      <x/>
-      <x v="114"/>
-    </i>
-    <i r="1">
-      <x v="123"/>
-      <x v="122"/>
-      <x v="2"/>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="22"/>
-      <x v="21"/>
-      <x v="22"/>
-      <x v="1"/>
-      <x v="74"/>
-    </i>
-    <i r="1">
-      <x v="36"/>
-      <x v="38"/>
-      <x/>
-      <x v="132"/>
-    </i>
-    <i r="1">
-      <x v="53"/>
-      <x v="55"/>
-      <x v="1"/>
-      <x v="75"/>
-    </i>
-    <i r="1">
-      <x v="70"/>
-      <x v="72"/>
-      <x v="1"/>
-      <x v="76"/>
-    </i>
-    <i r="1">
-      <x v="72"/>
-      <x v="73"/>
-      <x/>
-      <x v="103"/>
-    </i>
-    <i>
-      <x v="23"/>
       <x v="2"/>
       <x v="1"/>
       <x v="2"/>
@@ -6849,6 +6935,773 @@
       <x/>
       <x v="147"/>
     </i>
+    <i>
+      <x v="1"/>
+      <x v="21"/>
+      <x v="22"/>
+      <x v="1"/>
+      <x v="74"/>
+    </i>
+    <i r="1">
+      <x v="36"/>
+      <x v="38"/>
+      <x/>
+      <x v="132"/>
+    </i>
+    <i r="1">
+      <x v="53"/>
+      <x v="55"/>
+      <x v="1"/>
+      <x v="75"/>
+    </i>
+    <i r="1">
+      <x v="70"/>
+      <x v="72"/>
+      <x v="1"/>
+      <x v="76"/>
+    </i>
+    <i r="1">
+      <x v="72"/>
+      <x v="73"/>
+      <x/>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="89"/>
+      <x v="93"/>
+      <x v="1"/>
+      <x v="71"/>
+    </i>
+    <i r="1">
+      <x v="91"/>
+      <x v="91"/>
+      <x/>
+      <x v="135"/>
+    </i>
+    <i r="1">
+      <x v="118"/>
+      <x v="118"/>
+      <x v="1"/>
+      <x v="72"/>
+    </i>
+    <i r="1">
+      <x v="119"/>
+      <x v="119"/>
+      <x/>
+      <x v="117"/>
+    </i>
+    <i r="1">
+      <x v="120"/>
+      <x v="120"/>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="121"/>
+      <x v="121"/>
+      <x/>
+      <x v="114"/>
+    </i>
+    <i r="1">
+      <x v="123"/>
+      <x v="122"/>
+      <x v="2"/>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="5"/>
+      <x v="7"/>
+      <x v="1"/>
+      <x v="68"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+      <x v="6"/>
+      <x/>
+      <x v="138"/>
+    </i>
+    <i r="1">
+      <x v="44"/>
+      <x v="42"/>
+      <x/>
+      <x v="102"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+      <x v="47"/>
+      <x v="1"/>
+      <x v="69"/>
+    </i>
+    <i r="1">
+      <x v="49"/>
+      <x v="50"/>
+      <x/>
+      <x v="125"/>
+    </i>
+    <i r="1">
+      <x v="51"/>
+      <x v="52"/>
+      <x v="2"/>
+      <x v="67"/>
+    </i>
+    <i r="1">
+      <x v="52"/>
+      <x v="54"/>
+      <x/>
+      <x v="105"/>
+    </i>
+    <i r="1">
+      <x v="100"/>
+      <x v="100"/>
+      <x/>
+      <x v="131"/>
+    </i>
+    <i r="1">
+      <x v="101"/>
+      <x v="101"/>
+      <x/>
+      <x v="124"/>
+    </i>
+    <i r="1">
+      <x v="123"/>
+      <x v="123"/>
+      <x/>
+      <x v="127"/>
+    </i>
+    <i r="1">
+      <x v="124"/>
+      <x v="124"/>
+      <x/>
+      <x v="89"/>
+    </i>
+    <i r="1">
+      <x v="125"/>
+      <x v="126"/>
+      <x v="1"/>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="29"/>
+      <x v="28"/>
+      <x/>
+      <x v="143"/>
+    </i>
+    <i r="1">
+      <x v="31"/>
+      <x v="31"/>
+      <x v="1"/>
+      <x v="65"/>
+    </i>
+    <i r="1">
+      <x v="71"/>
+      <x v="72"/>
+      <x/>
+      <x v="128"/>
+    </i>
+    <i r="1">
+      <x v="75"/>
+      <x v="75"/>
+      <x v="1"/>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x v="21"/>
+      <x v="23"/>
+      <x v="1"/>
+      <x v="63"/>
+    </i>
+    <i r="1">
+      <x v="30"/>
+      <x v="46"/>
+      <x v="1"/>
+      <x v="64"/>
+    </i>
+    <i r="1">
+      <x v="37"/>
+      <x v="35"/>
+      <x/>
+      <x v="144"/>
+    </i>
+    <i>
+      <x v="6"/>
+      <x v="25"/>
+      <x v="26"/>
+      <x v="1"/>
+      <x v="58"/>
+    </i>
+    <i r="1">
+      <x v="32"/>
+      <x v="32"/>
+      <x v="2"/>
+      <x v="61"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+      <x v="57"/>
+      <x v="2"/>
+      <x v="62"/>
+    </i>
+    <i r="1">
+      <x v="73"/>
+      <x v="74"/>
+      <x v="1"/>
+      <x v="59"/>
+    </i>
+    <i r="1">
+      <x v="79"/>
+      <x v="81"/>
+      <x/>
+      <x v="130"/>
+    </i>
+    <i r="1">
+      <x v="80"/>
+      <x v="83"/>
+      <x v="1"/>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="7"/>
+      <x v="13"/>
+      <x v="14"/>
+      <x/>
+      <x v="116"/>
+    </i>
+    <i r="1">
+      <x v="14"/>
+      <x v="16"/>
+      <x v="1"/>
+      <x v="52"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+      <x v="30"/>
+      <x v="1"/>
+      <x v="53"/>
+    </i>
+    <i r="1">
+      <x v="54"/>
+      <x v="56"/>
+      <x v="1"/>
+      <x v="54"/>
+    </i>
+    <i r="1">
+      <x v="63"/>
+      <x v="69"/>
+      <x v="1"/>
+      <x v="55"/>
+    </i>
+    <i r="1">
+      <x v="96"/>
+      <x v="97"/>
+      <x v="1"/>
+      <x v="56"/>
+    </i>
+    <i r="1">
+      <x v="107"/>
+      <x v="105"/>
+      <x v="1"/>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="8"/>
+      <x v="4"/>
+      <x v="4"/>
+      <x v="1"/>
+      <x v="48"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+      <x v="9"/>
+      <x v="1"/>
+      <x v="49"/>
+    </i>
+    <i r="1">
+      <x v="42"/>
+      <x v="40"/>
+      <x/>
+      <x v="107"/>
+    </i>
+    <i r="1">
+      <x v="65"/>
+      <x v="67"/>
+      <x/>
+      <x v="108"/>
+    </i>
+    <i r="1">
+      <x v="77"/>
+      <x v="79"/>
+      <x v="1"/>
+      <x v="50"/>
+    </i>
+    <i r="1">
+      <x v="84"/>
+      <x v="85"/>
+      <x/>
+      <x v="118"/>
+    </i>
+    <i r="1">
+      <x v="103"/>
+      <x v="102"/>
+      <x v="1"/>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x v="81"/>
+      <x v="80"/>
+      <x/>
+      <x v="129"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x v="14"/>
+      <x v="15"/>
+      <x/>
+      <x v="140"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+      <x v="18"/>
+      <x v="2"/>
+      <x v="45"/>
+    </i>
+    <i r="1">
+      <x v="86"/>
+      <x v="87"/>
+      <x v="1"/>
+      <x v="46"/>
+    </i>
+    <i r="1">
+      <x v="87"/>
+      <x v="88"/>
+      <x/>
+      <x v="111"/>
+    </i>
+    <i r="1">
+      <x v="90"/>
+      <x v="90"/>
+      <x/>
+      <x v="142"/>
+    </i>
+    <i r="1">
+      <x v="94"/>
+      <x v="94"/>
+      <x v="2"/>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x v="46"/>
+      <x v="49"/>
+      <x v="1"/>
+      <x v="43"/>
+    </i>
+    <i r="1">
+      <x v="61"/>
+      <x v="61"/>
+      <x v="2"/>
+      <x v="44"/>
+    </i>
+    <i r="1">
+      <x v="62"/>
+      <x v="62"/>
+      <x/>
+      <x v="141"/>
+    </i>
+    <i>
+      <x v="12"/>
+      <x v="15"/>
+      <x v="17"/>
+      <x v="1"/>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="13"/>
+      <x v="8"/>
+      <x v="8"/>
+      <x/>
+      <x v="123"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+      <x v="10"/>
+      <x/>
+      <x v="96"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+      <x v="11"/>
+      <x v="1"/>
+      <x v="39"/>
+    </i>
+    <i r="1">
+      <x v="45"/>
+      <x v="43"/>
+      <x v="1"/>
+      <x v="40"/>
+    </i>
+    <i r="1">
+      <x v="56"/>
+      <x v="58"/>
+      <x/>
+      <x v="134"/>
+    </i>
+    <i r="1">
+      <x v="85"/>
+      <x v="86"/>
+      <x v="1"/>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="14"/>
+      <x v="2"/>
+      <x v="1"/>
+      <x/>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="15"/>
+      <x v="18"/>
+      <x v="19"/>
+      <x v="1"/>
+      <x v="33"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+      <x v="20"/>
+      <x/>
+      <x v="83"/>
+    </i>
+    <i r="1">
+      <x v="39"/>
+      <x v="37"/>
+      <x/>
+      <x v="120"/>
+    </i>
+    <i r="1">
+      <x v="40"/>
+      <x v="39"/>
+      <x v="1"/>
+      <x v="34"/>
+    </i>
+    <i r="1">
+      <x v="60"/>
+      <x v="64"/>
+      <x v="1"/>
+      <x v="35"/>
+    </i>
+    <i r="1">
+      <x v="74"/>
+      <x v="78"/>
+      <x v="1"/>
+      <x v="36"/>
+    </i>
+    <i r="1">
+      <x v="88"/>
+      <x v="89"/>
+      <x v="1"/>
+      <x v="37"/>
+    </i>
+    <i r="1">
+      <x v="95"/>
+      <x v="95"/>
+      <x/>
+      <x v="94"/>
+    </i>
+    <i r="1">
+      <x v="97"/>
+      <x v="96"/>
+      <x v="1"/>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="16"/>
+      <x v="38"/>
+      <x v="36"/>
+      <x v="1"/>
+      <x v="29"/>
+    </i>
+    <i r="1">
+      <x v="48"/>
+      <x v="53"/>
+      <x v="1"/>
+      <x v="30"/>
+    </i>
+    <i r="1">
+      <x v="63"/>
+      <x v="65"/>
+      <x v="2"/>
+      <x v="28"/>
+    </i>
+    <i r="1">
+      <x v="68"/>
+      <x v="76"/>
+      <x/>
+      <x v="99"/>
+    </i>
+    <i r="1">
+      <x v="69"/>
+      <x v="71"/>
+      <x/>
+      <x v="119"/>
+    </i>
+    <i r="1">
+      <x v="76"/>
+      <x v="77"/>
+      <x v="1"/>
+      <x v="31"/>
+    </i>
+    <i r="1">
+      <x v="108"/>
+      <x v="104"/>
+      <x v="1"/>
+      <x v="32"/>
+    </i>
+    <i r="1">
+      <x v="109"/>
+      <x v="106"/>
+      <x/>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="17"/>
+      <x v="17"/>
+      <x v="18"/>
+      <x v="1"/>
+      <x v="23"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+      <x v="24"/>
+      <x v="1"/>
+      <x v="24"/>
+    </i>
+    <i r="1">
+      <x v="41"/>
+      <x v="44"/>
+      <x v="1"/>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="50"/>
+      <x v="51"/>
+      <x v="2"/>
+      <x v="26"/>
+    </i>
+    <i r="1">
+      <x v="58"/>
+      <x v="59"/>
+      <x/>
+      <x v="109"/>
+    </i>
+    <i r="1">
+      <x v="82"/>
+      <x v="84"/>
+      <x v="1"/>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="18"/>
+      <x v="1"/>
+      <x/>
+      <x v="1"/>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+      <x v="12"/>
+      <x v="1"/>
+      <x v="19"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
+      <x v="18"/>
+      <x v="1"/>
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+      <x v="21"/>
+      <x/>
+      <x v="84"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+      <x v="45"/>
+      <x v="1"/>
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="66"/>
+      <x v="68"/>
+      <x v="2"/>
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="67"/>
+      <x v="70"/>
+      <x/>
+      <x v="106"/>
+    </i>
+    <i r="1">
+      <x v="98"/>
+      <x v="98"/>
+      <x/>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="19"/>
+      <x v="33"/>
+      <x v="33"/>
+      <x v="1"/>
+      <x v="15"/>
+    </i>
+    <i r="1">
+      <x v="35"/>
+      <x v="34"/>
+      <x/>
+      <x v="82"/>
+    </i>
+    <i r="1">
+      <x v="47"/>
+      <x v="48"/>
+      <x/>
+      <x v="85"/>
+    </i>
+    <i r="1">
+      <x v="55"/>
+      <x v="57"/>
+      <x v="1"/>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="78"/>
+      <x v="86"/>
+      <x v="1"/>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="83"/>
+      <x v="82"/>
+      <x/>
+      <x v="86"/>
+    </i>
+    <i r="1">
+      <x v="92"/>
+      <x v="92"/>
+      <x v="2"/>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="20"/>
+      <x/>
+      <x v="2"/>
+      <x v="1"/>
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+      <x v="13"/>
+      <x v="1"/>
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
+      <x v="17"/>
+      <x v="1"/>
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="20"/>
+      <x v="21"/>
+      <x/>
+      <x v="92"/>
+    </i>
+    <i r="1">
+      <x v="23"/>
+      <x v="25"/>
+      <x v="1"/>
+      <x v="13"/>
+    </i>
+    <i r="1">
+      <x v="34"/>
+      <x v="38"/>
+      <x v="1"/>
+      <x v="14"/>
+    </i>
+    <i r="1">
+      <x v="43"/>
+      <x v="41"/>
+      <x/>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="21"/>
+      <x v="7"/>
+      <x v="5"/>
+      <x v="1"/>
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="93"/>
+      <x v="95"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="22"/>
+      <x v="57"/>
+      <x v="63"/>
+      <x v="1"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="64"/>
+      <x v="66"/>
+      <x/>
+      <x v="146"/>
+    </i>
+    <i r="1">
+      <x v="111"/>
+      <x v="110"/>
+      <x v="1"/>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="113"/>
+      <x v="112"/>
+      <x v="1"/>
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="122"/>
+      <x v="121"/>
+      <x/>
+      <x v="122"/>
+    </i>
+    <i r="1">
+      <x v="126"/>
+      <x v="125"/>
+      <x/>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="23"/>
+      <x v="102"/>
+      <x v="107"/>
+      <x v="1"/>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="106"/>
+      <x v="103"/>
+      <x/>
+      <x v="137"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -6859,6 +7712,2942 @@
   <dataFields count="1">
     <dataField name="Sum of Duration (min)" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="141">
+    <format dxfId="281">
+      <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="4"/>
+    </format>
+    <format dxfId="280">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="279">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="102"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="107"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="278">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="106"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="103"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="137"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="277">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="57"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="63"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="276">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="64"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="66"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="146"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="275">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="111"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="110"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="274">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="113"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="112"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="273">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="122"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="121"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="122"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="272">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="126"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="125"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="87"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="271">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="270">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="93"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="95"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="269">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="268">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="267">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="266">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="92"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="265">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="25"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="264">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="34"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="38"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="263">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="43"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="41"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="97"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="262">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="33"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="33"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="15"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="261">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="35"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="34"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="82"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="260">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="47"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="48"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="85"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="259">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="55"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="57"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="16"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="258">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="78"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="86"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="257">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="83"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="82"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="86"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="256">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="92"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="92"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="255">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="254">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="253">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="84"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="45"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="21"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="66"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="68"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="22"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="67"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="70"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="106"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="98"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="98"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="104"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="24"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="24"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="41"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="44"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="50"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="51"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="26"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="58"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="59"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="109"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="82"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="84"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="27"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="38"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="36"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="29"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="240">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="48"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="53"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="30"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="239">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="63"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="65"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="28"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="238">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="68"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="76"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="99"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="69"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="71"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="119"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="76"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="77"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="31"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="235">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="108"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="104"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="32"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="234">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="109"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="106"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="110"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="233">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="33"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="232">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="19"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="83"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="231">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="39"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="37"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="120"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="230">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="40"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="39"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="34"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="229">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="60"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="64"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="35"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="228">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="74"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="78"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="36"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="227">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="88"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="89"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="37"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="226">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="95"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="95"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="94"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="225">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="97"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="96"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="38"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="224">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="121"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="223">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="123"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="222">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="96"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="221">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="39"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="220">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="45"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="43"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="40"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="219">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="56"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="58"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="134"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="218">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="85"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="86"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="41"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="217">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="12"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="216">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="46"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="49"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="215">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="61"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="61"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="214">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="62"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="62"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="141"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="213">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="15"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="140"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="212">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="17"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="18"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="45"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="211">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="86"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="87"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="210">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="87"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="88"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="111"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="209">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="90"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="90"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="142"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="208">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="94"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="94"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="207">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="81"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="80"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="129"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="206">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="48"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="205">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="49"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="204">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="42"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="40"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="107"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="203">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="65"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="67"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="108"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="202">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="77"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="79"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="201">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="84"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="85"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="118"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="200">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="103"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="102"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="51"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="199">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="13"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="116"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="198">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="14"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="16"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="52"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="197">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="30"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="53"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="196">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="54"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="56"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="54"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="195">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="63"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="69"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="55"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="194">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="96"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="97"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="56"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="193">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="107"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="105"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="57"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="192">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="25"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="26"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="58"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="191">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="32"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="32"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="61"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="190">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="55"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="57"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="62"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="189">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="73"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="74"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="59"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="188">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="79"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="81"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="130"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="187">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="80"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="83"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="60"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="186">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="23"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="63"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="185">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="30"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="46"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="64"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="184">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="37"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="35"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="144"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="183">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="29"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="28"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="143"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="182">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="31"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="31"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="65"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="181">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="71"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="72"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="128"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="180">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="75"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="75"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="66"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="179">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="68"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="178">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="138"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="177">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="44"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="42"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="102"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="176">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="47"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="47"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="69"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="175">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="49"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="50"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="125"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="174">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="51"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="52"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="67"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="173">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="52"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="54"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="105"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="172">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="100"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="100"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="131"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="171">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="101"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="101"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="124"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="170">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="123"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="123"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="127"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="169">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="124"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="124"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="89"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="168">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="125"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="126"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="70"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="167">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="89"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="93"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="71"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="166">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="91"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="91"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="135"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="165">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="118"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="118"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="72"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="164">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="119"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="119"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="117"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="163">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="120"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="120"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="162">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="121"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="121"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="114"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="161">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="123"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="122"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="73"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="160">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="21"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="22"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="74"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="159">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="36"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="38"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="132"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="158">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="53"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="55"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="75"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="157">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="70"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="72"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="76"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="156">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="72"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="73"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="103"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="155">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="81"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="154">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="113"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="153">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="27"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="27"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="98"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="152">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="28"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="29"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="77"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="151">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="59"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="60"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="136"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="150">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="99"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="99"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="126"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="149">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="104"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="102"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="148">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="105"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="109"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="78"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="147">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="110"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="108"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="79"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="146">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="112"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="111"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="80"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="145">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="114"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="113"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="145"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="144">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="115"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="114"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="10">
+            <x v="88"/>
+            <x v="90"/>
+            <x v="91"/>
+            <x v="93"/>
+            <x v="95"/>
+            <x v="100"/>
+            <x v="101"/>
+            <x v="112"/>
+            <x v="115"/>
+            <x v="139"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="143">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="115"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="115"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="133"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="142">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="116"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="116"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="141">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="5">
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="117"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="117"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="9" count="1">
+            <x v="147"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -7156,13 +10945,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2819D883-7DB3-46E8-8913-C2D163448CB4}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A3:F152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="136.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="61.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="128" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="129" max="129" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -7181,7 +10973,7 @@
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
@@ -7190,90 +10982,87 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>341</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
+        <v>86</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="F4" s="5">
-        <v>50</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
-        <v>21</v>
+      <c r="E5" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="F5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>351</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>353</v>
       </c>
       <c r="F7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>31</v>
+        <v>354</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="F8" s="5">
         <v>5</v>
@@ -7281,16 +11070,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="F9" s="5">
         <v>5</v>
@@ -7298,436 +11087,346 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>227</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="s">
-        <v>38</v>
+      <c r="E10" s="6" t="s">
+        <v>360</v>
       </c>
       <c r="F10" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>362</v>
       </c>
       <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="F11" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>44</v>
+      <c r="E12" s="6" t="s">
+        <v>368</v>
       </c>
       <c r="F12" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>369</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>369</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>47</v>
+        <v>18</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>370</v>
       </c>
       <c r="F13" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>371</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>371</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
+        <v>18</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>373</v>
       </c>
       <c r="F14" s="5">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>52</v>
+        <v>374</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>374</v>
       </c>
       <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>375</v>
       </c>
       <c r="F15" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>56</v>
+      <c r="E16" s="6" t="s">
+        <v>378</v>
       </c>
       <c r="F16" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" t="s">
-        <v>59</v>
+      <c r="E17" s="6" t="s">
+        <v>376</v>
       </c>
       <c r="F17" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
+      <c r="E18" s="6" t="s">
+        <v>379</v>
       </c>
       <c r="F18" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" t="s">
-        <v>65</v>
+      <c r="E19" s="6" t="s">
+        <v>387</v>
       </c>
       <c r="F19" s="5">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>67</v>
+      <c r="E20" s="6" t="s">
+        <v>380</v>
       </c>
       <c r="F20" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>70</v>
+      <c r="E21" s="6" t="s">
+        <v>381</v>
       </c>
       <c r="F21" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>72</v>
+      <c r="E22" s="6" t="s">
+        <v>382</v>
       </c>
       <c r="F22" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" t="s">
-        <v>74</v>
-      </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" t="s">
-        <v>76</v>
+      <c r="E23" s="6" t="s">
+        <v>389</v>
       </c>
       <c r="F23" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>78</v>
+      <c r="E24" s="6" t="s">
+        <v>386</v>
       </c>
       <c r="F24" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>383</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
+        <v>18</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>385</v>
       </c>
       <c r="F25" s="5">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>393</v>
       </c>
       <c r="F26" s="5">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>395</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" t="s">
-        <v>88</v>
+        <v>18</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>397</v>
       </c>
       <c r="F27" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>331</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="C28" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
-      <c r="E28" t="s">
-        <v>91</v>
+      <c r="E28" s="6" t="s">
+        <v>332</v>
       </c>
       <c r="F28" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>92</v>
+        <v>333</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>93</v>
+        <v>18</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>94</v>
+        <v>335</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>335</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
       </c>
-      <c r="E30" t="s">
-        <v>96</v>
+      <c r="E30" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="F30" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>57</v>
+        <v>337</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" t="s">
-        <v>97</v>
+        <v>13</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="F31" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" t="s">
-        <v>100</v>
+        <v>18</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="F32" s="5">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>316</v>
+      </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>318</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" t="s">
-        <v>102</v>
+        <v>13</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>319</v>
       </c>
       <c r="F33" s="5">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>320</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
-      <c r="E34" t="s">
-        <v>105</v>
+      <c r="E34" s="6" t="s">
+        <v>321</v>
       </c>
       <c r="F34" s="5">
         <v>5</v>
@@ -7735,36 +11434,33 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>322</v>
       </c>
       <c r="D35" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" t="s">
+        <v>324</v>
+      </c>
+      <c r="D36" t="s">
         <v>18</v>
       </c>
-      <c r="E35" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>108</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" t="s">
-        <v>109</v>
+      <c r="E36" s="6" t="s">
+        <v>325</v>
       </c>
       <c r="F36" s="5">
         <v>5</v>
@@ -7772,16 +11468,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>326</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" t="s">
-        <v>111</v>
+        <v>18</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>327</v>
       </c>
       <c r="F37" s="5">
         <v>5</v>
@@ -7789,87 +11485,87 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>112</v>
+        <v>328</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>114</v>
+        <v>18</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>329</v>
       </c>
       <c r="F38" s="5">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>115</v>
+        <v>306</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>306</v>
       </c>
       <c r="D39" t="s">
         <v>86</v>
       </c>
-      <c r="E39" t="s">
-        <v>117</v>
+      <c r="E39" s="6" t="s">
+        <v>330</v>
       </c>
       <c r="F39" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>284</v>
+      </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>285</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>286</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" t="s">
-        <v>119</v>
+        <v>13</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>287</v>
       </c>
       <c r="F40" s="5">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>120</v>
+        <v>288</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" t="s">
-        <v>122</v>
+        <v>18</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>291</v>
       </c>
       <c r="F41" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>123</v>
-      </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>292</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" t="s">
-        <v>125</v>
+        <v>18</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>293</v>
       </c>
       <c r="F42" s="5">
         <v>5</v>
@@ -7877,101 +11573,101 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" t="s">
         <v>126</v>
       </c>
-      <c r="C43" t="s">
-        <v>127</v>
-      </c>
       <c r="D43" t="s">
         <v>13</v>
       </c>
-      <c r="E43" t="s">
-        <v>128</v>
+      <c r="E43" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="F43" s="5">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>295</v>
       </c>
       <c r="D44" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" t="s">
-        <v>131</v>
+        <v>18</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="F44" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>297</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45" t="s">
-        <v>135</v>
+        <v>86</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>298</v>
       </c>
       <c r="F45" s="5">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>136</v>
+        <v>299</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="E46" t="s">
-        <v>138</v>
+      <c r="E46" s="6" t="s">
+        <v>301</v>
       </c>
       <c r="F46" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="C47" t="s">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" t="s">
-        <v>141</v>
+        <v>18</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="F47" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" t="s">
-        <v>143</v>
+        <v>18</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>305</v>
       </c>
       <c r="F48" s="5">
         <v>5</v>
@@ -7979,70 +11675,70 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>144</v>
+        <v>306</v>
       </c>
       <c r="C49" t="s">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
       </c>
-      <c r="E49" t="s">
-        <v>145</v>
+      <c r="E49" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F49" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>146</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>147</v>
+        <v>309</v>
       </c>
       <c r="C50" t="s">
-        <v>147</v>
+        <v>309</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" t="s">
-        <v>148</v>
+        <v>18</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="F50" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="C51" t="s">
-        <v>149</v>
+        <v>314</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" t="s">
-        <v>150</v>
+        <v>13</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>315</v>
       </c>
       <c r="F51" s="5">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>273</v>
+      </c>
       <c r="B52" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="C52" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
-      <c r="E52" t="s">
-        <v>153</v>
+      <c r="E52" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="F52" s="5">
         <v>5</v>
@@ -8050,101 +11746,104 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>277</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
       </c>
-      <c r="E53" t="s">
-        <v>155</v>
+      <c r="E53" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="F53" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="C54" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
-      </c>
-      <c r="E54" t="s">
-        <v>158</v>
+        <v>18</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="F54" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>159</v>
+        <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
       </c>
-      <c r="E55" t="s">
-        <v>161</v>
+      <c r="E55" s="6" t="s">
+        <v>283</v>
       </c>
       <c r="F55" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>264</v>
+      </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="C56" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="D56" t="s">
         <v>13</v>
       </c>
-      <c r="E56" t="s">
-        <v>164</v>
+      <c r="E56" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="F56" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>46</v>
+        <v>268</v>
       </c>
       <c r="C57" t="s">
-        <v>46</v>
+        <v>269</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" t="s">
-        <v>165</v>
+        <v>13</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="F57" s="5">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="C58" t="s">
-        <v>166</v>
+        <v>271</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" t="s">
-        <v>167</v>
+        <v>18</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="F58" s="5">
         <v>5</v>
@@ -8152,39 +11851,36 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="B59" t="s">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="C59" t="s">
-        <v>169</v>
+        <v>250</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" t="s">
-        <v>170</v>
+        <v>13</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="F59" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>171</v>
-      </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" t="s">
-        <v>174</v>
+        <v>86</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="F60" s="5">
         <v>5</v>
@@ -8192,212 +11888,209 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" t="s">
-        <v>177</v>
+        <v>86</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="F61" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>178</v>
+        <v>255</v>
       </c>
       <c r="C62" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
       </c>
-      <c r="E62" t="s">
-        <v>179</v>
+      <c r="E62" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="F62" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" t="s">
-        <v>181</v>
+        <v>18</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="F63" s="5">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>182</v>
+        <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="F64" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" t="s">
         <v>18</v>
       </c>
-      <c r="E64" t="s">
-        <v>184</v>
-      </c>
-      <c r="F64" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" t="s">
-        <v>185</v>
+      <c r="E65" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="F65" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>186</v>
-      </c>
+    <row r="66" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>55</v>
+        <v>198</v>
       </c>
       <c r="C66" t="s">
-        <v>55</v>
+        <v>234</v>
       </c>
       <c r="D66" t="s">
         <v>13</v>
       </c>
-      <c r="E66" t="s">
-        <v>187</v>
+      <c r="E66" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="F66" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>188</v>
-      </c>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="D67" t="s">
         <v>13</v>
       </c>
-      <c r="E67" t="s">
-        <v>191</v>
+      <c r="E67" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="F67" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="C68" t="s">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
-      </c>
-      <c r="E68" t="s">
-        <v>193</v>
+        <v>13</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="F68" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="C69" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>196</v>
+        <v>13</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="F69" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>197</v>
-      </c>
       <c r="B70" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="C70" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" t="s">
-        <v>199</v>
+        <v>13</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="F70" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="C71" t="s">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="D71" t="s">
-        <v>86</v>
-      </c>
-      <c r="E71" t="s">
-        <v>200</v>
+        <v>13</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="F71" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>212</v>
+      </c>
       <c r="B72" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
       </c>
-      <c r="E72" t="s">
-        <v>202</v>
+      <c r="E72" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="F72" s="5">
         <v>5</v>
@@ -8405,33 +12098,33 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" t="s">
-        <v>204</v>
+        <v>13</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="F73" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
-      <c r="E74" t="s">
-        <v>206</v>
+      <c r="E74" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="F74" s="5">
         <v>5</v>
@@ -8439,56 +12132,50 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
-      </c>
-      <c r="E75" t="s">
-        <v>208</v>
+        <v>18</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>220</v>
       </c>
       <c r="F75" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>209</v>
-      </c>
       <c r="B76" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" t="s">
-        <v>211</v>
+        <v>13</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="F76" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>212</v>
-      </c>
       <c r="B77" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C77" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" t="s">
-        <v>214</v>
+        <v>18</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="F77" s="5">
         <v>5</v>
@@ -8496,84 +12183,90 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="D78" t="s">
         <v>13</v>
       </c>
-      <c r="E78" t="s">
-        <v>216</v>
+      <c r="E78" s="6" t="s">
+        <v>228</v>
       </c>
       <c r="F78" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>209</v>
+      </c>
       <c r="B79" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
       </c>
-      <c r="E79" t="s">
-        <v>218</v>
+      <c r="E79" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="F79" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>197</v>
+      </c>
       <c r="B80" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
       </c>
-      <c r="E80" t="s">
-        <v>220</v>
+      <c r="E80" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="F80" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="C81" t="s">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" t="s">
-        <v>222</v>
+        <v>86</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="F81" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="C82" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" t="s">
-        <v>225</v>
+        <v>13</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="F82" s="5">
         <v>5</v>
@@ -8581,36 +12274,33 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="C83" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="D83" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" t="s">
-        <v>228</v>
+        <v>18</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="F83" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>229</v>
-      </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="C84" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
-      <c r="E84" t="s">
-        <v>233</v>
+      <c r="E84" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="F84" s="5">
         <v>5</v>
@@ -8618,50 +12308,53 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C85" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" t="s">
-        <v>235</v>
+        <v>86</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="F85" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>188</v>
+      </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="C86" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="D86" t="s">
         <v>13</v>
       </c>
-      <c r="E86" t="s">
-        <v>238</v>
+      <c r="E86" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="F86" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" t="s">
-        <v>240</v>
+        <v>86</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="F87" s="5">
         <v>5</v>
@@ -8669,87 +12362,90 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
-      </c>
-      <c r="E88" t="s">
-        <v>242</v>
+        <v>18</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="F88" s="5">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>186</v>
+      </c>
       <c r="B89" t="s">
-        <v>243</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>244</v>
+        <v>55</v>
       </c>
       <c r="D89" t="s">
         <v>13</v>
       </c>
-      <c r="E89" t="s">
-        <v>245</v>
+      <c r="E89" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="F89" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>171</v>
+      </c>
       <c r="B90" t="s">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
-      </c>
-      <c r="E90" t="s">
-        <v>248</v>
+        <v>18</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="F90" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>249</v>
-      </c>
       <c r="B91" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="C91" t="s">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="D91" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s">
-        <v>251</v>
+        <v>18</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="F91" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
+        <v>178</v>
       </c>
       <c r="D92" t="s">
-        <v>86</v>
-      </c>
-      <c r="E92" t="s">
-        <v>253</v>
+        <v>13</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="F92" s="5">
         <v>5</v>
@@ -8757,16 +12453,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="C93" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
-      </c>
-      <c r="E93" t="s">
-        <v>254</v>
+        <v>13</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="F93" s="5">
         <v>5</v>
@@ -8774,16 +12470,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>255</v>
+        <v>182</v>
       </c>
       <c r="C94" t="s">
-        <v>256</v>
+        <v>182</v>
       </c>
       <c r="D94" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" t="s">
-        <v>257</v>
+        <v>18</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="F94" s="5">
         <v>5</v>
@@ -8791,314 +12487,314 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="C95" t="s">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F95" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>168</v>
+      </c>
+      <c r="B96" t="s">
+        <v>169</v>
+      </c>
+      <c r="C96" t="s">
+        <v>169</v>
+      </c>
+      <c r="D96" t="s">
         <v>18</v>
       </c>
-      <c r="E95" t="s">
-        <v>260</v>
-      </c>
-      <c r="F95" s="5">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>261</v>
-      </c>
-      <c r="C96" t="s">
-        <v>262</v>
-      </c>
-      <c r="D96" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" t="s">
-        <v>263</v>
+      <c r="E96" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="F96" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>264</v>
+        <v>146</v>
       </c>
       <c r="B97" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="C97" t="s">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
       </c>
-      <c r="E97" t="s">
-        <v>267</v>
+      <c r="E97" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="F97" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>268</v>
+        <v>149</v>
       </c>
       <c r="C98" t="s">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="D98" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" t="s">
-        <v>270</v>
+        <v>18</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="F98" s="5">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="C99" t="s">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
       </c>
-      <c r="E99" t="s">
-        <v>272</v>
+      <c r="E99" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="F99" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>273</v>
-      </c>
+    <row r="100" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>274</v>
+        <v>154</v>
       </c>
       <c r="C100" t="s">
-        <v>274</v>
+        <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
-      </c>
-      <c r="E100" t="s">
-        <v>275</v>
+        <v>13</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="F100" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>276</v>
+        <v>156</v>
       </c>
       <c r="C101" t="s">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="D101" t="s">
         <v>13</v>
       </c>
-      <c r="E101" t="s">
-        <v>278</v>
+      <c r="E101" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="F101" s="5">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="C102" t="s">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="D102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F102" s="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>162</v>
+      </c>
+      <c r="C103" t="s">
+        <v>163</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F103" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" t="s">
         <v>18</v>
       </c>
-      <c r="E102" t="s">
-        <v>280</v>
-      </c>
-      <c r="F102" s="5">
+      <c r="E104" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F104" s="5">
         <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B103" t="s">
-        <v>281</v>
-      </c>
-      <c r="C103" t="s">
-        <v>282</v>
-      </c>
-      <c r="D103" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" t="s">
-        <v>283</v>
-      </c>
-      <c r="F103" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>284</v>
-      </c>
-      <c r="B104" t="s">
-        <v>285</v>
-      </c>
-      <c r="C104" t="s">
-        <v>286</v>
-      </c>
-      <c r="D104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>287</v>
-      </c>
-      <c r="F104" s="5">
-        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>288</v>
+        <v>166</v>
       </c>
       <c r="C105" t="s">
-        <v>289</v>
+        <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" t="s">
-        <v>291</v>
+        <v>13</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="F105" s="5">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
       <c r="B106" t="s">
-        <v>292</v>
+        <v>124</v>
       </c>
       <c r="C106" t="s">
-        <v>292</v>
+        <v>124</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
-      </c>
-      <c r="E106" t="s">
-        <v>293</v>
+        <v>13</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="F106" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D107" t="s">
         <v>13</v>
       </c>
-      <c r="E107" t="s">
-        <v>294</v>
+      <c r="E107" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="F107" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>295</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>295</v>
+        <v>130</v>
       </c>
       <c r="D108" t="s">
+        <v>86</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F108" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>132</v>
+      </c>
+      <c r="C109" t="s">
+        <v>133</v>
+      </c>
+      <c r="D109" t="s">
         <v>18</v>
       </c>
-      <c r="E108" t="s">
-        <v>296</v>
-      </c>
-      <c r="F108" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
-        <v>297</v>
-      </c>
-      <c r="C109" t="s">
-        <v>297</v>
-      </c>
-      <c r="D109" t="s">
-        <v>86</v>
-      </c>
-      <c r="E109" t="s">
-        <v>298</v>
+      <c r="E109" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="F109" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>299</v>
+        <v>136</v>
       </c>
       <c r="C110" t="s">
-        <v>300</v>
+        <v>136</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
       </c>
-      <c r="E110" t="s">
-        <v>301</v>
+      <c r="E110" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="F110" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>302</v>
+        <v>139</v>
       </c>
       <c r="C111" t="s">
-        <v>302</v>
+        <v>140</v>
       </c>
       <c r="D111" t="s">
-        <v>18</v>
-      </c>
-      <c r="E111" t="s">
-        <v>303</v>
+        <v>13</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="F111" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>304</v>
+        <v>142</v>
       </c>
       <c r="C112" t="s">
-        <v>304</v>
+        <v>142</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
-      </c>
-      <c r="E112" t="s">
-        <v>305</v>
+        <v>13</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="F112" s="5">
         <v>5</v>
@@ -9106,87 +12802,87 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>306</v>
+        <v>144</v>
       </c>
       <c r="C113" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="D113" t="s">
         <v>18</v>
       </c>
-      <c r="E113" t="s">
-        <v>308</v>
+      <c r="E113" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="F113" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>108</v>
+      </c>
       <c r="B114" t="s">
-        <v>309</v>
+        <v>95</v>
       </c>
       <c r="C114" t="s">
-        <v>309</v>
+        <v>95</v>
       </c>
       <c r="D114" t="s">
-        <v>18</v>
-      </c>
-      <c r="E114" t="s">
-        <v>312</v>
+        <v>13</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="F114" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>313</v>
+        <v>110</v>
       </c>
       <c r="C115" t="s">
-        <v>314</v>
+        <v>110</v>
       </c>
       <c r="D115" t="s">
         <v>13</v>
       </c>
-      <c r="E115" t="s">
-        <v>315</v>
+      <c r="E115" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="F115" s="5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>316</v>
-      </c>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>317</v>
+        <v>112</v>
       </c>
       <c r="C116" t="s">
-        <v>318</v>
+        <v>113</v>
       </c>
       <c r="D116" t="s">
         <v>13</v>
       </c>
-      <c r="E116" t="s">
-        <v>319</v>
+      <c r="E116" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="F116" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>320</v>
+        <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>320</v>
+        <v>116</v>
       </c>
       <c r="D117" t="s">
-        <v>18</v>
-      </c>
-      <c r="E117" t="s">
-        <v>321</v>
+        <v>86</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="F117" s="5">
         <v>5</v>
@@ -9194,50 +12890,53 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>322</v>
+        <v>118</v>
       </c>
       <c r="C118" t="s">
-        <v>322</v>
+        <v>118</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" t="s">
-        <v>323</v>
+        <v>18</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="F118" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>324</v>
+        <v>120</v>
       </c>
       <c r="C119" t="s">
-        <v>324</v>
+        <v>121</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
-      </c>
-      <c r="E119" t="s">
-        <v>325</v>
+        <v>13</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="F119" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>89</v>
+      </c>
       <c r="B120" t="s">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="C120" t="s">
-        <v>326</v>
+        <v>90</v>
       </c>
       <c r="D120" t="s">
-        <v>18</v>
-      </c>
-      <c r="E120" t="s">
-        <v>327</v>
+        <v>13</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F120" s="5">
         <v>5</v>
@@ -9245,87 +12944,84 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>328</v>
+        <v>92</v>
       </c>
       <c r="C121" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D121" t="s">
-        <v>18</v>
-      </c>
-      <c r="E121" t="s">
-        <v>329</v>
+        <v>13</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F121" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="C122" t="s">
-        <v>306</v>
+        <v>95</v>
       </c>
       <c r="D122" t="s">
-        <v>86</v>
-      </c>
-      <c r="E122" t="s">
-        <v>330</v>
+        <v>13</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="F122" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>331</v>
-      </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>57</v>
       </c>
       <c r="C123" t="s">
-        <v>265</v>
+        <v>57</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" t="s">
-        <v>332</v>
+        <v>18</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="F123" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>333</v>
+        <v>98</v>
       </c>
       <c r="C124" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" t="s">
-        <v>334</v>
+        <v>13</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="F124" s="5">
-        <v>16</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="C125" t="s">
-        <v>335</v>
+        <v>101</v>
       </c>
       <c r="D125" t="s">
-        <v>13</v>
-      </c>
-      <c r="E125" t="s">
-        <v>336</v>
+        <v>86</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="F125" s="5">
         <v>5</v>
@@ -9333,33 +13029,33 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>337</v>
+        <v>103</v>
       </c>
       <c r="C126" t="s">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
-      </c>
-      <c r="E126" t="s">
-        <v>338</v>
+        <v>18</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="F126" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="C127" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="D127" t="s">
         <v>18</v>
       </c>
-      <c r="E127" t="s">
-        <v>340</v>
+      <c r="E127" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="F127" s="5">
         <v>5</v>
@@ -9367,341 +13063,441 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>341</v>
+        <v>68</v>
       </c>
       <c r="B128" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="C128" t="s">
-        <v>169</v>
+        <v>69</v>
       </c>
       <c r="D128" t="s">
-        <v>86</v>
-      </c>
-      <c r="E128" t="s">
-        <v>344</v>
+        <v>13</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="F128" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>345</v>
+        <v>71</v>
       </c>
       <c r="C129" t="s">
-        <v>346</v>
+        <v>71</v>
       </c>
       <c r="D129" t="s">
         <v>18</v>
       </c>
-      <c r="E129" t="s">
-        <v>348</v>
+      <c r="E129" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F129" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>349</v>
+        <v>73</v>
       </c>
       <c r="C130" t="s">
-        <v>349</v>
+        <v>74</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
       </c>
-      <c r="E130" t="s">
-        <v>350</v>
+      <c r="E130" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="F130" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>77</v>
+      </c>
+      <c r="C131" t="s">
+        <v>77</v>
+      </c>
+      <c r="D131" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F131" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
-        <v>351</v>
-      </c>
-      <c r="C131" t="s">
-        <v>352</v>
-      </c>
-      <c r="D131" t="s">
-        <v>13</v>
-      </c>
-      <c r="E131" t="s">
-        <v>353</v>
-      </c>
-      <c r="F131" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>354</v>
+        <v>79</v>
       </c>
       <c r="C132" t="s">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="D132" t="s">
-        <v>18</v>
-      </c>
-      <c r="E132" t="s">
-        <v>355</v>
+        <v>13</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F132" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="C133" t="s">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="D133" t="s">
         <v>18</v>
       </c>
-      <c r="E133" t="s">
-        <v>358</v>
+      <c r="E133" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="F133" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>227</v>
+        <v>84</v>
       </c>
       <c r="C134" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
-      </c>
-      <c r="E134" t="s">
-        <v>360</v>
+        <v>86</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="F134" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>48</v>
+      </c>
       <c r="B135" t="s">
-        <v>361</v>
+        <v>49</v>
       </c>
       <c r="C135" t="s">
-        <v>362</v>
+        <v>50</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
       </c>
-      <c r="E135" t="s">
-        <v>363</v>
+      <c r="E135" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="F135" s="5">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="136" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>364</v>
-      </c>
       <c r="C136" t="s">
-        <v>365</v>
+        <v>53</v>
       </c>
       <c r="D136" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" t="s">
-        <v>368</v>
+        <v>13</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="F136" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137" spans="2:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>369</v>
+        <v>55</v>
       </c>
       <c r="C137" t="s">
-        <v>369</v>
+        <v>55</v>
       </c>
       <c r="D137" t="s">
-        <v>18</v>
-      </c>
-      <c r="E137" t="s">
-        <v>370</v>
+        <v>13</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="F137" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>371</v>
+        <v>57</v>
       </c>
       <c r="C138" t="s">
-        <v>371</v>
+        <v>57</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
       </c>
-      <c r="E138" t="s">
-        <v>373</v>
+      <c r="E138" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="F138" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>374</v>
+        <v>60</v>
       </c>
       <c r="C139" t="s">
-        <v>374</v>
+        <v>61</v>
       </c>
       <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F139" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>63</v>
+      </c>
+      <c r="C140" t="s">
+        <v>64</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F140" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>66</v>
+      </c>
+      <c r="C141" t="s">
+        <v>66</v>
+      </c>
+      <c r="D141" t="s">
         <v>18</v>
       </c>
-      <c r="E139" t="s">
-        <v>375</v>
-      </c>
-      <c r="F139" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E140" t="s">
-        <v>378</v>
-      </c>
-      <c r="F140" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="141" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E141" t="s">
-        <v>376</v>
+      <c r="E141" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="F141" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E142" t="s">
-        <v>379</v>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>42</v>
+      </c>
+      <c r="B142" t="s">
+        <v>43</v>
+      </c>
+      <c r="C142" t="s">
+        <v>43</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="F142" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="143" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E143" t="s">
-        <v>387</v>
+    <row r="143" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>45</v>
+      </c>
+      <c r="C143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="F143" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E144" t="s">
-        <v>380</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>22</v>
+      </c>
+      <c r="B144" t="s">
+        <v>23</v>
+      </c>
+      <c r="C144" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="F144" s="5">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E145" t="s">
-        <v>381</v>
+      <c r="B145" t="s">
+        <v>27</v>
+      </c>
+      <c r="C145" t="s">
+        <v>27</v>
+      </c>
+      <c r="D145" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="F145" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E146" t="s">
-        <v>382</v>
+      <c r="B146" t="s">
+        <v>31</v>
+      </c>
+      <c r="C146" t="s">
+        <v>31</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="F146" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E147" t="s">
-        <v>389</v>
+      <c r="B147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C147" t="s">
+        <v>33</v>
+      </c>
+      <c r="D147" t="s">
+        <v>13</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="F147" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E148" t="s">
-        <v>386</v>
+      <c r="B148" t="s">
+        <v>35</v>
+      </c>
+      <c r="C148" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="F148" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>39</v>
+      </c>
       <c r="C149" t="s">
-        <v>383</v>
+        <v>39</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
       </c>
-      <c r="E149" t="s">
-        <v>385</v>
+      <c r="E149" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="F149" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>10</v>
+      </c>
       <c r="B150" t="s">
-        <v>390</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>391</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
-        <v>86</v>
-      </c>
-      <c r="E150" t="s">
-        <v>393</v>
+        <v>13</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="F150" s="5">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>394</v>
+        <v>17</v>
       </c>
       <c r="C151" t="s">
-        <v>395</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
         <v>18</v>
       </c>
-      <c r="E151" t="s">
-        <v>397</v>
+      <c r="E151" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="F151" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
+      <c r="A152" s="6" t="s">
         <v>1029</v>
       </c>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="6"/>
       <c r="F152" s="5">
         <v>1360</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="71" fitToHeight="0" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
